--- a/experiments/results/abp/cplex-cp-abp.xlsx
+++ b/experiments/results/abp/cplex-cp-abp.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.24</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>323.3</t>
+          <t>315.8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>208.7</t>
+          <t>249.4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>132.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>132.4</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.03</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1389,20 +1389,24 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>181</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>195.1</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>708.04</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1442,22 +1446,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1515,7 +1519,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1562,7 +1566,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1572,7 +1576,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>187.6</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1630,12 +1634,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>141.9</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>755.27</t>
+          <t>265.93</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1682,22 +1686,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>178.0</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1750,12 +1754,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>110.3</t>
+          <t>105.8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1807,17 +1811,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>211.1</t>
+          <t>205.1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1870,12 +1874,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>206.7</t>
+          <t>202.4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1923,17 +1927,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>239.4</t>
+          <t>237.2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2062,12 +2066,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2124,12 +2128,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2186,12 +2190,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2248,12 +2252,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2310,12 +2314,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2372,12 +2376,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2434,12 +2438,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2496,12 +2500,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>183.23</t>
+          <t>149.11</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2553,17 +2557,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>188.1</t>
+          <t>220.6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -2616,12 +2620,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>128.9</t>
+          <t>146.6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.01</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -2674,12 +2678,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2736,12 +2740,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2793,17 +2797,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>152.9</t>
+          <t>176.7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.05</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2851,17 +2855,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>176.4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -2904,22 +2908,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>251</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>180.6</t>
+          <t>197.2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2962,22 +2966,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>165.8</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -3030,12 +3034,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>112.6</t>
+          <t>116.1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>133.20</t>
+          <t>118.05</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3087,17 +3091,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.01</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -3150,12 +3154,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>183.2</t>
+          <t>180.8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.07</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3198,22 +3202,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>219.3</t>
+          <t>239.9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3266,12 +3270,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>144.6</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>65.39</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3328,12 +3332,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>240.3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.10</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3376,7 +3380,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3386,12 +3390,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>258.4</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3439,17 +3443,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>276.4</t>
+          <t>285.9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.11</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3558,35 +3562,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>569.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3616,32 +3624,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>74.43</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -3678,35 +3686,39 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>637.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3736,35 +3748,39 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>412.7</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3794,35 +3810,39 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>476.1</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3852,32 +3872,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3914,35 +3934,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>409.0</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3972,35 +3996,39 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>962.01</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4030,35 +4058,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>546.7</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4088,35 +4120,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>281.7</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4146,35 +4182,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>180.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4204,12 +4244,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4224,12 +4264,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -4266,27 +4306,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>240.1</t>
+          <t>148.1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4324,32 +4364,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>239.6</t>
+          <t>149.1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -4382,35 +4422,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>361</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>655.4</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4440,27 +4484,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>330.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4498,35 +4542,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>455</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>319.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4556,32 +4604,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>302.8</t>
+          <t>344.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -4614,35 +4662,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>262</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>279.3</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4672,35 +4724,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>340</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>402.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>9.58</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4730,32 +4786,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>193.1</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>70.13</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -4792,35 +4848,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>675</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>385.0</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4850,32 +4910,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>299</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>454.6</t>
+          <t>257.6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.03</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -4908,32 +4968,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>216</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>581</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>476.3</t>
+          <t>239.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -5042,35 +5102,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>436.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5100,32 +5164,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -5162,32 +5226,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -5224,32 +5288,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -5286,32 +5350,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -5348,32 +5412,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -5410,32 +5474,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>145.83</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -5472,27 +5536,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>333.4</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -5530,35 +5594,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>542.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5588,35 +5656,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>299.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5646,35 +5718,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>127</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5704,12 +5780,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5724,12 +5800,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5766,32 +5842,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>233.4</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -5824,27 +5900,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>235.8</t>
+          <t>172.7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5882,35 +5958,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>451</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>451</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>429.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5940,32 +6020,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>557</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>227</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>308.1</t>
+          <t>204.3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -5998,35 +6078,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>567</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6056,12 +6140,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>629</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6071,17 +6155,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>312.9</t>
+          <t>278.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -6114,35 +6198,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>327</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>265.5</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6172,35 +6260,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>424</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>411.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>55.65</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6230,32 +6322,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>826</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>826</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>191.7</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>79.05</t>
+          <t>58.47</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6292,35 +6384,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>412</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>386.4</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6350,17 +6446,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>857</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>342</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6370,12 +6466,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>387.1</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -6408,32 +6504,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>726</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>410.3</t>
+          <t>268.9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -6542,35 +6638,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>402.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6600,32 +6700,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -6662,32 +6762,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -6724,32 +6824,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -6786,32 +6886,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -6848,32 +6948,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -6910,32 +7010,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>242.45</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -6972,12 +7072,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6987,17 +7087,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>379.6</t>
+          <t>432.2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -7030,35 +7130,39 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>605.6</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7088,35 +7192,39 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>105</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>285.4</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7146,35 +7254,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>153</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>136.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7204,12 +7316,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -7224,12 +7336,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -7266,32 +7378,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>172.7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.05</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -7324,32 +7436,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>271.7</t>
+          <t>173.9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.05</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -7382,35 +7494,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>541</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>548.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7440,32 +7556,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>437.1</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -7498,35 +7614,39 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>681</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>681</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>224.3</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7556,32 +7676,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>191</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>331.4</t>
+          <t>312.3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.05</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -7614,35 +7734,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>392</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7672,35 +7796,39 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>508</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>508</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>443.3</t>
+          <t>110.2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>80.36</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7730,32 +7858,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>331</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>993</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>991</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>991</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>251.2</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>197.93</t>
+          <t>85.65</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -7792,35 +7920,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>494</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>494</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>419.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7850,17 +7982,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>412</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -7870,12 +8002,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>449.7</t>
+          <t>297.9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -7908,32 +8040,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>329</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>451.4</t>
+          <t>340.7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
